--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188815</v>
+        <v>113188802</v>
       </c>
       <c r="B11" t="n">
-        <v>88614</v>
+        <v>91292</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1593</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751433</v>
+        <v>751434</v>
       </c>
       <c r="R11" t="n">
-        <v>7216110</v>
+        <v>7216028</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188813</v>
+        <v>113188807</v>
       </c>
       <c r="B12" t="n">
-        <v>91313</v>
+        <v>91294</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751414</v>
+        <v>751440</v>
       </c>
       <c r="R12" t="n">
-        <v>7215828</v>
+        <v>7215963</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188806</v>
+        <v>113188809</v>
       </c>
       <c r="B13" t="n">
-        <v>91278</v>
+        <v>91349</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751463</v>
+        <v>751418</v>
       </c>
       <c r="R13" t="n">
-        <v>7216194</v>
+        <v>7215786</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188816</v>
+        <v>113188805</v>
       </c>
       <c r="B14" t="n">
-        <v>91278</v>
+        <v>91294</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751441</v>
+        <v>751456</v>
       </c>
       <c r="R14" t="n">
-        <v>7216188</v>
+        <v>7216208</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,7 +2122,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2141,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188809</v>
+        <v>113188813</v>
       </c>
       <c r="B15" t="n">
-        <v>91333</v>
+        <v>91329</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751418</v>
+        <v>751414</v>
       </c>
       <c r="R15" t="n">
-        <v>7215786</v>
+        <v>7215828</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188807</v>
+        <v>113188808</v>
       </c>
       <c r="B16" t="n">
-        <v>91278</v>
+        <v>91294</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751440</v>
+        <v>751409</v>
       </c>
       <c r="R16" t="n">
-        <v>7215963</v>
+        <v>7215886</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188808</v>
+        <v>113188806</v>
       </c>
       <c r="B17" t="n">
-        <v>91278</v>
+        <v>91294</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751409</v>
+        <v>751463</v>
       </c>
       <c r="R17" t="n">
-        <v>7215886</v>
+        <v>7216194</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188811</v>
+        <v>113188804</v>
       </c>
       <c r="B18" t="n">
-        <v>96267</v>
+        <v>91292</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751288</v>
+        <v>751437</v>
       </c>
       <c r="R18" t="n">
-        <v>7215704</v>
+        <v>7216004</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,7 +2591,7 @@
         <v>113188822</v>
       </c>
       <c r="B19" t="n">
-        <v>91284</v>
+        <v>91300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188804</v>
+        <v>113188815</v>
       </c>
       <c r="B20" t="n">
-        <v>91276</v>
+        <v>88630</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2712,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>1593</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751437</v>
+        <v>751433</v>
       </c>
       <c r="R20" t="n">
-        <v>7216004</v>
+        <v>7216110</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188810</v>
+        <v>113188811</v>
       </c>
       <c r="B21" t="n">
-        <v>91302</v>
+        <v>96283</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2828,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751419</v>
+        <v>751288</v>
       </c>
       <c r="R21" t="n">
-        <v>7215911</v>
+        <v>7215704</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188812</v>
+        <v>113188810</v>
       </c>
       <c r="B22" t="n">
-        <v>91313</v>
+        <v>91318</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751435</v>
+        <v>751419</v>
       </c>
       <c r="R22" t="n">
-        <v>7216128</v>
+        <v>7215911</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188818</v>
+        <v>113188812</v>
       </c>
       <c r="B23" t="n">
-        <v>88654</v>
+        <v>91329</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3048,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751449</v>
+        <v>751435</v>
       </c>
       <c r="R23" t="n">
-        <v>7215930</v>
+        <v>7216128</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188802</v>
+        <v>113188818</v>
       </c>
       <c r="B24" t="n">
-        <v>91276</v>
+        <v>88670</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751434</v>
+        <v>751449</v>
       </c>
       <c r="R24" t="n">
-        <v>7216028</v>
+        <v>7215930</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,7 +3263,7 @@
         <v>113188801</v>
       </c>
       <c r="B25" t="n">
-        <v>91276</v>
+        <v>91292</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3373,10 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188805</v>
+        <v>113188816</v>
       </c>
       <c r="B26" t="n">
-        <v>91278</v>
+        <v>91294</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751456</v>
+        <v>751441</v>
       </c>
       <c r="R26" t="n">
-        <v>7216208</v>
+        <v>7216188</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,6 +3466,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188802</v>
+        <v>113188807</v>
       </c>
       <c r="B11" t="n">
-        <v>91292</v>
+        <v>91294</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751434</v>
+        <v>751440</v>
       </c>
       <c r="R11" t="n">
-        <v>7216028</v>
+        <v>7215963</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188807</v>
+        <v>113188802</v>
       </c>
       <c r="B12" t="n">
-        <v>91294</v>
+        <v>91292</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751440</v>
+        <v>751434</v>
       </c>
       <c r="R12" t="n">
-        <v>7215963</v>
+        <v>7216028</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188810</v>
+        <v>113188812</v>
       </c>
       <c r="B22" t="n">
-        <v>91318</v>
+        <v>91329</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751419</v>
+        <v>751435</v>
       </c>
       <c r="R22" t="n">
-        <v>7215911</v>
+        <v>7216128</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188812</v>
+        <v>113188818</v>
       </c>
       <c r="B23" t="n">
-        <v>91329</v>
+        <v>88670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751435</v>
+        <v>751449</v>
       </c>
       <c r="R23" t="n">
-        <v>7216128</v>
+        <v>7215930</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188818</v>
+        <v>113188810</v>
       </c>
       <c r="B24" t="n">
-        <v>88670</v>
+        <v>91318</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751449</v>
+        <v>751419</v>
       </c>
       <c r="R24" t="n">
-        <v>7215930</v>
+        <v>7215911</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188807</v>
+        <v>113188813</v>
       </c>
       <c r="B11" t="n">
-        <v>91294</v>
+        <v>91329</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751440</v>
+        <v>751414</v>
       </c>
       <c r="R11" t="n">
-        <v>7215963</v>
+        <v>7215828</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188809</v>
+        <v>113188801</v>
       </c>
       <c r="B13" t="n">
-        <v>91349</v>
+        <v>91292</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751418</v>
+        <v>751431</v>
       </c>
       <c r="R13" t="n">
-        <v>7215786</v>
+        <v>7216140</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188805</v>
+        <v>113188810</v>
       </c>
       <c r="B14" t="n">
-        <v>91294</v>
+        <v>91318</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751456</v>
+        <v>751419</v>
       </c>
       <c r="R14" t="n">
-        <v>7216208</v>
+        <v>7215911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188813</v>
+        <v>113188805</v>
       </c>
       <c r="B15" t="n">
-        <v>91329</v>
+        <v>91294</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751414</v>
+        <v>751456</v>
       </c>
       <c r="R15" t="n">
-        <v>7215828</v>
+        <v>7216208</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188808</v>
+        <v>113188811</v>
       </c>
       <c r="B16" t="n">
-        <v>91294</v>
+        <v>96283</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751409</v>
+        <v>751288</v>
       </c>
       <c r="R16" t="n">
-        <v>7215886</v>
+        <v>7215704</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188806</v>
+        <v>113188812</v>
       </c>
       <c r="B17" t="n">
-        <v>91294</v>
+        <v>91329</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751463</v>
+        <v>751435</v>
       </c>
       <c r="R17" t="n">
-        <v>7216194</v>
+        <v>7216128</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188804</v>
+        <v>113188815</v>
       </c>
       <c r="B18" t="n">
-        <v>91292</v>
+        <v>88630</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3100</v>
+        <v>1593</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751437</v>
+        <v>751433</v>
       </c>
       <c r="R18" t="n">
-        <v>7216004</v>
+        <v>7216110</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188815</v>
+        <v>113188807</v>
       </c>
       <c r="B20" t="n">
-        <v>88630</v>
+        <v>91294</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2716,21 +2716,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1593</v>
+        <v>149</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751433</v>
+        <v>751440</v>
       </c>
       <c r="R20" t="n">
-        <v>7216110</v>
+        <v>7215963</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188811</v>
+        <v>113188816</v>
       </c>
       <c r="B21" t="n">
-        <v>96283</v>
+        <v>91294</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,25 +2824,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>149</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751288</v>
+        <v>751441</v>
       </c>
       <c r="R21" t="n">
-        <v>7215704</v>
+        <v>7216188</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,6 +2906,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2924,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188812</v>
+        <v>113188809</v>
       </c>
       <c r="B22" t="n">
-        <v>91329</v>
+        <v>91349</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,21 +2941,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751435</v>
+        <v>751418</v>
       </c>
       <c r="R22" t="n">
-        <v>7216128</v>
+        <v>7215786</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2999,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3009,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188818</v>
+        <v>113188808</v>
       </c>
       <c r="B23" t="n">
-        <v>88670</v>
+        <v>91294</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751449</v>
+        <v>751409</v>
       </c>
       <c r="R23" t="n">
-        <v>7215930</v>
+        <v>7215886</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3111,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3121,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188810</v>
+        <v>113188804</v>
       </c>
       <c r="B24" t="n">
-        <v>91318</v>
+        <v>91292</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3160,25 +3161,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751419</v>
+        <v>751437</v>
       </c>
       <c r="R24" t="n">
-        <v>7215911</v>
+        <v>7216004</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3223,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188801</v>
+        <v>113188806</v>
       </c>
       <c r="B25" t="n">
-        <v>91292</v>
+        <v>91294</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3272,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751431</v>
+        <v>751463</v>
       </c>
       <c r="R25" t="n">
-        <v>7216140</v>
+        <v>7216194</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3335,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188816</v>
+        <v>113188818</v>
       </c>
       <c r="B26" t="n">
-        <v>91294</v>
+        <v>88670</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3388,21 +3389,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751441</v>
+        <v>751449</v>
       </c>
       <c r="R26" t="n">
-        <v>7216188</v>
+        <v>7215930</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3447,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3466,7 +3467,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1695,7 +1695,7 @@
         <v>113188813</v>
       </c>
       <c r="B11" t="n">
-        <v>91329</v>
+        <v>91341</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188802</v>
+        <v>113188805</v>
       </c>
       <c r="B12" t="n">
-        <v>91292</v>
+        <v>91306</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751434</v>
+        <v>751456</v>
       </c>
       <c r="R12" t="n">
-        <v>7216028</v>
+        <v>7216208</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188801</v>
+        <v>113188806</v>
       </c>
       <c r="B13" t="n">
-        <v>91292</v>
+        <v>91306</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751431</v>
+        <v>751463</v>
       </c>
       <c r="R13" t="n">
-        <v>7216140</v>
+        <v>7216194</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188810</v>
+        <v>113188808</v>
       </c>
       <c r="B14" t="n">
-        <v>91318</v>
+        <v>91306</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751419</v>
+        <v>751409</v>
       </c>
       <c r="R14" t="n">
-        <v>7215911</v>
+        <v>7215886</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188805</v>
+        <v>113188801</v>
       </c>
       <c r="B15" t="n">
-        <v>91294</v>
+        <v>91304</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751456</v>
+        <v>751431</v>
       </c>
       <c r="R15" t="n">
-        <v>7216208</v>
+        <v>7216140</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188811</v>
+        <v>113188816</v>
       </c>
       <c r="B16" t="n">
-        <v>96283</v>
+        <v>91306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>149</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751288</v>
+        <v>751441</v>
       </c>
       <c r="R16" t="n">
-        <v>7215704</v>
+        <v>7216188</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,6 +2346,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2364,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188812</v>
+        <v>113188815</v>
       </c>
       <c r="B17" t="n">
-        <v>91329</v>
+        <v>88642</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2377,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>1593</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751435</v>
+        <v>751433</v>
       </c>
       <c r="R17" t="n">
-        <v>7216128</v>
+        <v>7216110</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188815</v>
+        <v>113188811</v>
       </c>
       <c r="B18" t="n">
-        <v>88630</v>
+        <v>96295</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,25 +2489,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1593</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751433</v>
+        <v>751288</v>
       </c>
       <c r="R18" t="n">
-        <v>7216110</v>
+        <v>7215704</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188822</v>
+        <v>113188802</v>
       </c>
       <c r="B19" t="n">
-        <v>91300</v>
+        <v>91304</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,21 +2605,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751441</v>
+        <v>751434</v>
       </c>
       <c r="R19" t="n">
-        <v>7216183</v>
+        <v>7216028</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188807</v>
+        <v>113188812</v>
       </c>
       <c r="B20" t="n">
-        <v>91294</v>
+        <v>91341</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,25 +2713,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751440</v>
+        <v>751435</v>
       </c>
       <c r="R20" t="n">
-        <v>7215963</v>
+        <v>7216128</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2775,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2785,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188816</v>
+        <v>113188809</v>
       </c>
       <c r="B21" t="n">
-        <v>91294</v>
+        <v>91361</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2824,25 +2825,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751441</v>
+        <v>751418</v>
       </c>
       <c r="R21" t="n">
-        <v>7216188</v>
+        <v>7215786</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2887,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2897,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2906,7 +2907,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188809</v>
+        <v>113188810</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>91330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751418</v>
+        <v>751419</v>
       </c>
       <c r="R22" t="n">
-        <v>7215786</v>
+        <v>7215911</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188808</v>
+        <v>113188818</v>
       </c>
       <c r="B23" t="n">
-        <v>91294</v>
+        <v>88682</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751409</v>
+        <v>751449</v>
       </c>
       <c r="R23" t="n">
-        <v>7215886</v>
+        <v>7215930</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>113188804</v>
       </c>
       <c r="B24" t="n">
-        <v>91292</v>
+        <v>91304</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188806</v>
+        <v>113188807</v>
       </c>
       <c r="B25" t="n">
-        <v>91294</v>
+        <v>91306</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751463</v>
+        <v>751440</v>
       </c>
       <c r="R25" t="n">
-        <v>7216194</v>
+        <v>7215963</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188818</v>
+        <v>113188822</v>
       </c>
       <c r="B26" t="n">
-        <v>88670</v>
+        <v>91312</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751449</v>
+        <v>751441</v>
       </c>
       <c r="R26" t="n">
-        <v>7215930</v>
+        <v>7216183</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188813</v>
+        <v>113188818</v>
       </c>
       <c r="B11" t="n">
-        <v>91341</v>
+        <v>88682</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751414</v>
+        <v>751449</v>
       </c>
       <c r="R11" t="n">
-        <v>7215828</v>
+        <v>7215930</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188805</v>
+        <v>113188810</v>
       </c>
       <c r="B12" t="n">
-        <v>91306</v>
+        <v>91330</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751456</v>
+        <v>751419</v>
       </c>
       <c r="R12" t="n">
-        <v>7216208</v>
+        <v>7215911</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188806</v>
+        <v>113188801</v>
       </c>
       <c r="B13" t="n">
-        <v>91306</v>
+        <v>91304</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751463</v>
+        <v>751431</v>
       </c>
       <c r="R13" t="n">
-        <v>7216194</v>
+        <v>7216140</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,7 +2028,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188808</v>
+        <v>113188805</v>
       </c>
       <c r="B14" t="n">
         <v>91306</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751409</v>
+        <v>751456</v>
       </c>
       <c r="R14" t="n">
-        <v>7215886</v>
+        <v>7216208</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188801</v>
+        <v>113188811</v>
       </c>
       <c r="B15" t="n">
-        <v>91304</v>
+        <v>96295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3100</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751431</v>
+        <v>751288</v>
       </c>
       <c r="R15" t="n">
-        <v>7216140</v>
+        <v>7215704</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188816</v>
+        <v>113188812</v>
       </c>
       <c r="B16" t="n">
-        <v>91306</v>
+        <v>91341</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751441</v>
+        <v>751435</v>
       </c>
       <c r="R16" t="n">
-        <v>7216188</v>
+        <v>7216128</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,7 +2346,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2365,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188815</v>
+        <v>113188804</v>
       </c>
       <c r="B17" t="n">
-        <v>88642</v>
+        <v>91304</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1593</v>
+        <v>3100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751433</v>
+        <v>751437</v>
       </c>
       <c r="R17" t="n">
-        <v>7216110</v>
+        <v>7216004</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188811</v>
+        <v>113188822</v>
       </c>
       <c r="B18" t="n">
-        <v>96295</v>
+        <v>91312</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751288</v>
+        <v>751441</v>
       </c>
       <c r="R18" t="n">
-        <v>7215704</v>
+        <v>7216183</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188802</v>
+        <v>113188816</v>
       </c>
       <c r="B19" t="n">
-        <v>91304</v>
+        <v>91306</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,25 +2600,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751434</v>
+        <v>751441</v>
       </c>
       <c r="R19" t="n">
-        <v>7216028</v>
+        <v>7216188</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,6 +2682,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188812</v>
+        <v>113188807</v>
       </c>
       <c r="B20" t="n">
-        <v>91341</v>
+        <v>91306</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,25 +2713,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751435</v>
+        <v>751440</v>
       </c>
       <c r="R20" t="n">
-        <v>7216128</v>
+        <v>7215963</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188809</v>
+        <v>113188813</v>
       </c>
       <c r="B21" t="n">
-        <v>91361</v>
+        <v>91341</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751418</v>
+        <v>751414</v>
       </c>
       <c r="R21" t="n">
-        <v>7215786</v>
+        <v>7215828</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188810</v>
+        <v>113188806</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91306</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751419</v>
+        <v>751463</v>
       </c>
       <c r="R22" t="n">
-        <v>7215911</v>
+        <v>7216194</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188818</v>
+        <v>113188802</v>
       </c>
       <c r="B23" t="n">
-        <v>88682</v>
+        <v>91304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751449</v>
+        <v>751434</v>
       </c>
       <c r="R23" t="n">
-        <v>7215930</v>
+        <v>7216028</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188804</v>
+        <v>113188809</v>
       </c>
       <c r="B24" t="n">
-        <v>91304</v>
+        <v>91361</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751437</v>
+        <v>751418</v>
       </c>
       <c r="R24" t="n">
-        <v>7216004</v>
+        <v>7215786</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188807</v>
+        <v>113188815</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>88642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>149</v>
+        <v>1593</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751440</v>
+        <v>751433</v>
       </c>
       <c r="R25" t="n">
-        <v>7215963</v>
+        <v>7216110</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188822</v>
+        <v>113188808</v>
       </c>
       <c r="B26" t="n">
-        <v>91312</v>
+        <v>91306</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751441</v>
+        <v>751409</v>
       </c>
       <c r="R26" t="n">
-        <v>7216183</v>
+        <v>7215886</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188802</v>
+        <v>113188809</v>
       </c>
       <c r="B23" t="n">
-        <v>91304</v>
+        <v>91361</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751434</v>
+        <v>751418</v>
       </c>
       <c r="R23" t="n">
-        <v>7216028</v>
+        <v>7215786</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188809</v>
+        <v>113188802</v>
       </c>
       <c r="B24" t="n">
-        <v>91361</v>
+        <v>91304</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3165,21 +3165,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751418</v>
+        <v>751434</v>
       </c>
       <c r="R24" t="n">
-        <v>7215786</v>
+        <v>7216028</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188815</v>
+        <v>113188808</v>
       </c>
       <c r="B25" t="n">
-        <v>88642</v>
+        <v>91306</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1593</v>
+        <v>149</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751433</v>
+        <v>751409</v>
       </c>
       <c r="R25" t="n">
-        <v>7216110</v>
+        <v>7215886</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188808</v>
+        <v>113188815</v>
       </c>
       <c r="B26" t="n">
-        <v>91306</v>
+        <v>88642</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>1593</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751409</v>
+        <v>751433</v>
       </c>
       <c r="R26" t="n">
-        <v>7215886</v>
+        <v>7216110</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188818</v>
+        <v>113188806</v>
       </c>
       <c r="B11" t="n">
-        <v>88682</v>
+        <v>91328</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751449</v>
+        <v>751463</v>
       </c>
       <c r="R11" t="n">
-        <v>7215930</v>
+        <v>7216194</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188810</v>
+        <v>113188802</v>
       </c>
       <c r="B12" t="n">
-        <v>91330</v>
+        <v>91326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751419</v>
+        <v>751434</v>
       </c>
       <c r="R12" t="n">
-        <v>7215911</v>
+        <v>7216028</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188801</v>
+        <v>113188812</v>
       </c>
       <c r="B13" t="n">
-        <v>91304</v>
+        <v>91363</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,21 +1932,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751431</v>
+        <v>751435</v>
       </c>
       <c r="R13" t="n">
-        <v>7216140</v>
+        <v>7216128</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188805</v>
+        <v>113188813</v>
       </c>
       <c r="B14" t="n">
-        <v>91306</v>
+        <v>91363</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751456</v>
+        <v>751414</v>
       </c>
       <c r="R14" t="n">
-        <v>7216208</v>
+        <v>7215828</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188811</v>
+        <v>113188810</v>
       </c>
       <c r="B15" t="n">
-        <v>96295</v>
+        <v>91352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751288</v>
+        <v>751419</v>
       </c>
       <c r="R15" t="n">
-        <v>7215704</v>
+        <v>7215911</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188812</v>
+        <v>113188807</v>
       </c>
       <c r="B16" t="n">
-        <v>91341</v>
+        <v>91328</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751435</v>
+        <v>751440</v>
       </c>
       <c r="R16" t="n">
-        <v>7216128</v>
+        <v>7215963</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188804</v>
+        <v>113188816</v>
       </c>
       <c r="B17" t="n">
-        <v>91304</v>
+        <v>91328</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751437</v>
+        <v>751441</v>
       </c>
       <c r="R17" t="n">
-        <v>7216004</v>
+        <v>7216188</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,6 +2458,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2476,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188822</v>
+        <v>113188815</v>
       </c>
       <c r="B18" t="n">
-        <v>91312</v>
+        <v>88664</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2488,25 +2489,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751441</v>
+        <v>751433</v>
       </c>
       <c r="R18" t="n">
-        <v>7216183</v>
+        <v>7216110</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2551,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188816</v>
+        <v>113188811</v>
       </c>
       <c r="B19" t="n">
-        <v>91306</v>
+        <v>96317</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,25 +2601,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>149</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751441</v>
+        <v>751288</v>
       </c>
       <c r="R19" t="n">
-        <v>7216188</v>
+        <v>7215704</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2663,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2673,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2682,7 +2683,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188807</v>
+        <v>113188808</v>
       </c>
       <c r="B20" t="n">
-        <v>91306</v>
+        <v>91328</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751440</v>
+        <v>751409</v>
       </c>
       <c r="R20" t="n">
-        <v>7215963</v>
+        <v>7215886</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188813</v>
+        <v>113188804</v>
       </c>
       <c r="B21" t="n">
-        <v>91341</v>
+        <v>91326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2829,21 +2829,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751414</v>
+        <v>751437</v>
       </c>
       <c r="R21" t="n">
-        <v>7215828</v>
+        <v>7216004</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188806</v>
+        <v>113188818</v>
       </c>
       <c r="B22" t="n">
-        <v>91306</v>
+        <v>88704</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,21 +2941,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751463</v>
+        <v>751449</v>
       </c>
       <c r="R22" t="n">
-        <v>7216194</v>
+        <v>7215930</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188809</v>
+        <v>113188822</v>
       </c>
       <c r="B23" t="n">
-        <v>91361</v>
+        <v>91334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751418</v>
+        <v>751441</v>
       </c>
       <c r="R23" t="n">
-        <v>7215786</v>
+        <v>7216183</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188802</v>
+        <v>113188801</v>
       </c>
       <c r="B24" t="n">
-        <v>91304</v>
+        <v>91326</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751434</v>
+        <v>751431</v>
       </c>
       <c r="R24" t="n">
-        <v>7216028</v>
+        <v>7216140</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188808</v>
+        <v>113188809</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>91383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751409</v>
+        <v>751418</v>
       </c>
       <c r="R25" t="n">
-        <v>7215886</v>
+        <v>7215786</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188815</v>
+        <v>113188805</v>
       </c>
       <c r="B26" t="n">
-        <v>88642</v>
+        <v>91328</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1593</v>
+        <v>149</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751433</v>
+        <v>751456</v>
       </c>
       <c r="R26" t="n">
-        <v>7216110</v>
+        <v>7216208</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1916,7 +1916,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188812</v>
+        <v>113188813</v>
       </c>
       <c r="B13" t="n">
         <v>91363</v>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751435</v>
+        <v>751414</v>
       </c>
       <c r="R13" t="n">
-        <v>7216128</v>
+        <v>7215828</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188813</v>
+        <v>113188810</v>
       </c>
       <c r="B14" t="n">
-        <v>91363</v>
+        <v>91352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751414</v>
+        <v>751419</v>
       </c>
       <c r="R14" t="n">
-        <v>7215828</v>
+        <v>7215911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188810</v>
+        <v>113188812</v>
       </c>
       <c r="B15" t="n">
-        <v>91352</v>
+        <v>91363</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751419</v>
+        <v>751435</v>
       </c>
       <c r="R15" t="n">
-        <v>7215911</v>
+        <v>7216128</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188806</v>
+        <v>113188807</v>
       </c>
       <c r="B11" t="n">
-        <v>91328</v>
+        <v>91332</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751463</v>
+        <v>751440</v>
       </c>
       <c r="R11" t="n">
-        <v>7216194</v>
+        <v>7215963</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188802</v>
+        <v>113188808</v>
       </c>
       <c r="B12" t="n">
-        <v>91326</v>
+        <v>91332</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,25 +1816,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751434</v>
+        <v>751409</v>
       </c>
       <c r="R12" t="n">
-        <v>7216028</v>
+        <v>7215886</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188813</v>
+        <v>113188810</v>
       </c>
       <c r="B13" t="n">
-        <v>91363</v>
+        <v>91356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751414</v>
+        <v>751419</v>
       </c>
       <c r="R13" t="n">
-        <v>7215828</v>
+        <v>7215911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188810</v>
+        <v>113188822</v>
       </c>
       <c r="B14" t="n">
-        <v>91352</v>
+        <v>91338</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2040,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751419</v>
+        <v>751441</v>
       </c>
       <c r="R14" t="n">
-        <v>7215911</v>
+        <v>7216183</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188812</v>
+        <v>113188816</v>
       </c>
       <c r="B15" t="n">
-        <v>91363</v>
+        <v>91332</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>149</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751435</v>
+        <v>751441</v>
       </c>
       <c r="R15" t="n">
-        <v>7216128</v>
+        <v>7216188</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,6 +2234,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2252,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188807</v>
+        <v>113188815</v>
       </c>
       <c r="B16" t="n">
-        <v>91328</v>
+        <v>88668</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>149</v>
+        <v>1593</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751440</v>
+        <v>751433</v>
       </c>
       <c r="R16" t="n">
-        <v>7215963</v>
+        <v>7216110</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113188816</v>
+        <v>113188813</v>
       </c>
       <c r="B17" t="n">
-        <v>91328</v>
+        <v>91367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2377,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751441</v>
+        <v>751414</v>
       </c>
       <c r="R17" t="n">
-        <v>7216188</v>
+        <v>7215828</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2439,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2449,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,7 +2459,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188815</v>
+        <v>113188818</v>
       </c>
       <c r="B18" t="n">
-        <v>88664</v>
+        <v>88708</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1593</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751433</v>
+        <v>751449</v>
       </c>
       <c r="R18" t="n">
-        <v>7216110</v>
+        <v>7215930</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188811</v>
+        <v>113188802</v>
       </c>
       <c r="B19" t="n">
-        <v>96317</v>
+        <v>91330</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,25 +2601,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751288</v>
+        <v>751434</v>
       </c>
       <c r="R19" t="n">
-        <v>7215704</v>
+        <v>7216028</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188808</v>
+        <v>113188806</v>
       </c>
       <c r="B20" t="n">
-        <v>91328</v>
+        <v>91332</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751409</v>
+        <v>751463</v>
       </c>
       <c r="R20" t="n">
-        <v>7215886</v>
+        <v>7216194</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113188804</v>
+        <v>113188805</v>
       </c>
       <c r="B21" t="n">
-        <v>91326</v>
+        <v>91332</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,25 +2825,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751437</v>
+        <v>751456</v>
       </c>
       <c r="R21" t="n">
-        <v>7216004</v>
+        <v>7216208</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188818</v>
+        <v>113188804</v>
       </c>
       <c r="B22" t="n">
-        <v>88704</v>
+        <v>91330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751449</v>
+        <v>751437</v>
       </c>
       <c r="R22" t="n">
-        <v>7215930</v>
+        <v>7216004</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188822</v>
+        <v>113188812</v>
       </c>
       <c r="B23" t="n">
-        <v>91334</v>
+        <v>91367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751441</v>
+        <v>751435</v>
       </c>
       <c r="R23" t="n">
-        <v>7216183</v>
+        <v>7216128</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113188801</v>
+        <v>113188811</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>96321</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,25 +3161,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3100</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751431</v>
+        <v>751288</v>
       </c>
       <c r="R24" t="n">
-        <v>7216140</v>
+        <v>7215704</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188809</v>
+        <v>113188801</v>
       </c>
       <c r="B25" t="n">
-        <v>91383</v>
+        <v>91330</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751418</v>
+        <v>751431</v>
       </c>
       <c r="R25" t="n">
-        <v>7215786</v>
+        <v>7216140</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188805</v>
+        <v>113188809</v>
       </c>
       <c r="B26" t="n">
-        <v>91328</v>
+        <v>91387</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751456</v>
+        <v>751418</v>
       </c>
       <c r="R26" t="n">
-        <v>7216208</v>
+        <v>7215786</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188812</v>
+        <v>113188801</v>
       </c>
       <c r="B23" t="n">
-        <v>91367</v>
+        <v>91330</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3053,21 +3053,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5966</v>
+        <v>3100</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751435</v>
+        <v>751431</v>
       </c>
       <c r="R23" t="n">
-        <v>7216128</v>
+        <v>7216140</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113188801</v>
+        <v>113188812</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>91367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3277,21 +3277,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3100</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751431</v>
+        <v>751435</v>
       </c>
       <c r="R25" t="n">
-        <v>7216140</v>
+        <v>7216128</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188807</v>
+        <v>113188804</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>91336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751440</v>
+        <v>751437</v>
       </c>
       <c r="R11" t="n">
-        <v>7215963</v>
+        <v>7216004</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188808</v>
+        <v>113188806</v>
       </c>
       <c r="B12" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751409</v>
+        <v>751463</v>
       </c>
       <c r="R12" t="n">
-        <v>7215886</v>
+        <v>7216194</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188810</v>
+        <v>113188808</v>
       </c>
       <c r="B13" t="n">
-        <v>91356</v>
+        <v>91338</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>751419</v>
+        <v>751409</v>
       </c>
       <c r="R13" t="n">
-        <v>7215911</v>
+        <v>7215886</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113188822</v>
+        <v>113188809</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>91393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>751441</v>
+        <v>751418</v>
       </c>
       <c r="R14" t="n">
-        <v>7216183</v>
+        <v>7215786</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113188816</v>
+        <v>113188807</v>
       </c>
       <c r="B15" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>751441</v>
+        <v>751440</v>
       </c>
       <c r="R15" t="n">
-        <v>7216188</v>
+        <v>7215963</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2234,7 +2234,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2253,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113188815</v>
+        <v>113188801</v>
       </c>
       <c r="B16" t="n">
-        <v>88668</v>
+        <v>91336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1593</v>
+        <v>3100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751433</v>
+        <v>751431</v>
       </c>
       <c r="R16" t="n">
-        <v>7216110</v>
+        <v>7216140</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,7 +2367,7 @@
         <v>113188813</v>
       </c>
       <c r="B17" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2477,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113188818</v>
+        <v>113188802</v>
       </c>
       <c r="B18" t="n">
-        <v>88708</v>
+        <v>91336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2489,25 +2488,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751449</v>
+        <v>751434</v>
       </c>
       <c r="R18" t="n">
-        <v>7215930</v>
+        <v>7216028</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113188802</v>
+        <v>113188816</v>
       </c>
       <c r="B19" t="n">
-        <v>91330</v>
+        <v>91338</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,25 +2600,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2629,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>751434</v>
+        <v>751441</v>
       </c>
       <c r="R19" t="n">
-        <v>7216028</v>
+        <v>7216188</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2673,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2683,6 +2682,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113188806</v>
+        <v>113188818</v>
       </c>
       <c r="B20" t="n">
-        <v>91332</v>
+        <v>88714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,21 +2717,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>751463</v>
+        <v>751449</v>
       </c>
       <c r="R20" t="n">
-        <v>7216194</v>
+        <v>7215930</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2816,7 +2816,7 @@
         <v>113188805</v>
       </c>
       <c r="B21" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113188804</v>
+        <v>113188810</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91362</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751437</v>
+        <v>751419</v>
       </c>
       <c r="R22" t="n">
-        <v>7216004</v>
+        <v>7215911</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113188801</v>
+        <v>113188815</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>88674</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3100</v>
+        <v>1593</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751431</v>
+        <v>751433</v>
       </c>
       <c r="R23" t="n">
-        <v>7216140</v>
+        <v>7216110</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,7 +3152,7 @@
         <v>113188811</v>
       </c>
       <c r="B24" t="n">
-        <v>96321</v>
+        <v>96327</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>113188812</v>
       </c>
       <c r="B25" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113188809</v>
+        <v>113188822</v>
       </c>
       <c r="B26" t="n">
-        <v>91387</v>
+        <v>91344</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751418</v>
+        <v>751441</v>
       </c>
       <c r="R26" t="n">
-        <v>7215786</v>
+        <v>7216183</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3483,6 +3483,123 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114729840</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56446</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gråliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>751419</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7215738</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,6 +3842,2475 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118965905</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91772</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bankera fuligineoalba</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kälmyran (Kälmyran), Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>751429</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7215674</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118966040</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kälmyran (Kälmyran), Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>751426</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7215728</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118967787</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91778</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>751437</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7216044</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118966618</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>751464</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7215896</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118967351</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91802</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>751417</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7215928</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118968543</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96814</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>751544</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7215969</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118968519</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>751550</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7215986</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118967847</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>751445</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7216038</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118966592</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56502</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>751460</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7215876</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118965998</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kälmyran (Kälmyran), Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>751413</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7215668</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118966695</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91778</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>751436</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7215935</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118968088</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>751436</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7216165</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118967385</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>751378</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7215987</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118967650</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86231</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>249254</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mospindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius areni-silvae</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Brandrud) Brandrud</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>751418</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7216025</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118967018</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>751426</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7215942</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118968364</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91798</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>751471</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7216039</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>118967384</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>751387</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7215965</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>118966801</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>751425</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7215914</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>118968115</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>751449</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7216169</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>118967904</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91412</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>751433</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7216048</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>118967968</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>751409</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7216099</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118966665</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91780</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gråliden (Gråliden), Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>751413</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7215913</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Sara Forsström , Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 899-2023 artfynd.xlsx
+++ b/artfynd/A 899-2023 artfynd.xlsx
@@ -3844,10 +3844,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118965905</v>
+        <v>118968115</v>
       </c>
       <c r="B30" t="n">
-        <v>91772</v>
+        <v>91780</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3860,34 +3860,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kälmyran (Kälmyran), Vb</t>
+          <t>Gråliden (Gråliden), Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>751429</v>
+        <v>751449</v>
       </c>
       <c r="R30" t="n">
-        <v>7215674</v>
+        <v>7216169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3956,7 +3956,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118966040</v>
+        <v>118965998</v>
       </c>
       <c r="B31" t="n">
         <v>91780</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>751426</v>
+        <v>751413</v>
       </c>
       <c r="R31" t="n">
-        <v>7215728</v>
+        <v>7215668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4068,10 +4068,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118967787</v>
+        <v>118967650</v>
       </c>
       <c r="B32" t="n">
-        <v>91778</v>
+        <v>86231</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>249254</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mospindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius areni-silvae</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brandrud) Brandrud</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>751437</v>
+        <v>751418</v>
       </c>
       <c r="R32" t="n">
-        <v>7216044</v>
+        <v>7216025</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,10 +4180,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118966618</v>
+        <v>118967787</v>
       </c>
       <c r="B33" t="n">
-        <v>91412</v>
+        <v>91778</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4196,21 +4196,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4220,10 +4220,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>751464</v>
+        <v>751437</v>
       </c>
       <c r="R33" t="n">
-        <v>7215896</v>
+        <v>7216044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118967351</v>
+        <v>118967847</v>
       </c>
       <c r="B34" t="n">
-        <v>91802</v>
+        <v>91412</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4308,21 +4308,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>751417</v>
+        <v>751445</v>
       </c>
       <c r="R34" t="n">
-        <v>7215928</v>
+        <v>7216038</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4404,10 +4404,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118968543</v>
+        <v>118968088</v>
       </c>
       <c r="B35" t="n">
-        <v>96814</v>
+        <v>91780</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4416,25 +4416,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>751544</v>
+        <v>751436</v>
       </c>
       <c r="R35" t="n">
-        <v>7215969</v>
+        <v>7216165</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4516,7 +4516,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118968519</v>
+        <v>118967968</v>
       </c>
       <c r="B36" t="n">
         <v>91780</v>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>751550</v>
+        <v>751409</v>
       </c>
       <c r="R36" t="n">
-        <v>7215986</v>
+        <v>7216099</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4628,10 +4628,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118967847</v>
+        <v>118966801</v>
       </c>
       <c r="B37" t="n">
-        <v>91412</v>
+        <v>91780</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>751445</v>
+        <v>751425</v>
       </c>
       <c r="R37" t="n">
-        <v>7216038</v>
+        <v>7215914</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118966592</v>
+        <v>118967904</v>
       </c>
       <c r="B38" t="n">
-        <v>56502</v>
+        <v>91412</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4752,43 +4752,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gråliden (Gråliden), Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>751460</v>
+        <v>751433</v>
       </c>
       <c r="R38" t="n">
-        <v>7215876</v>
+        <v>7216048</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4820,7 +4815,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4830,7 +4825,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4857,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118965998</v>
+        <v>118966695</v>
       </c>
       <c r="B39" t="n">
-        <v>91780</v>
+        <v>91778</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4873,34 +4868,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kälmyran (Kälmyran), Vb</t>
+          <t>Gråliden (Gråliden), Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>751413</v>
+        <v>751436</v>
       </c>
       <c r="R39" t="n">
-        <v>7215668</v>
+        <v>7215935</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4932,7 +4927,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4942,7 +4937,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4969,10 +4964,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118966695</v>
+        <v>118967385</v>
       </c>
       <c r="B40" t="n">
-        <v>91778</v>
+        <v>91780</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4985,21 +4980,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5009,10 +5004,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>751436</v>
+        <v>751378</v>
       </c>
       <c r="R40" t="n">
-        <v>7215935</v>
+        <v>7215987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5044,7 +5039,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5054,7 +5049,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118968088</v>
+        <v>118968364</v>
       </c>
       <c r="B41" t="n">
-        <v>91780</v>
+        <v>91798</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5093,25 +5088,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>751436</v>
+        <v>751471</v>
       </c>
       <c r="R41" t="n">
-        <v>7216165</v>
+        <v>7216039</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,7 +5151,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5166,7 +5161,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5193,10 +5188,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118967385</v>
+        <v>118965905</v>
       </c>
       <c r="B42" t="n">
-        <v>91780</v>
+        <v>91772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5209,34 +5204,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gråliden (Gråliden), Vb</t>
+          <t>Kälmyran (Kälmyran), Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>751378</v>
+        <v>751429</v>
       </c>
       <c r="R42" t="n">
-        <v>7215987</v>
+        <v>7215674</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5268,7 +5263,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5278,7 +5273,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5305,10 +5300,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118967650</v>
+        <v>118968519</v>
       </c>
       <c r="B43" t="n">
-        <v>86231</v>
+        <v>91780</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5321,21 +5316,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>249254</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mospindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius areni-silvae</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brandrud) Brandrud</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5345,10 +5340,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>751418</v>
+        <v>751550</v>
       </c>
       <c r="R43" t="n">
-        <v>7216025</v>
+        <v>7215986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5380,7 +5375,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5390,7 +5385,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5417,10 +5412,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118967018</v>
+        <v>118966592</v>
       </c>
       <c r="B44" t="n">
-        <v>91412</v>
+        <v>56502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5429,38 +5424,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4745</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gråliden (Gråliden), Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>751426</v>
+        <v>751460</v>
       </c>
       <c r="R44" t="n">
-        <v>7215942</v>
+        <v>7215876</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5529,10 +5529,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118968364</v>
+        <v>118966040</v>
       </c>
       <c r="B45" t="n">
-        <v>91798</v>
+        <v>91780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5541,38 +5541,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gråliden (Gråliden), Vb</t>
+          <t>Kälmyran (Kälmyran), Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>751471</v>
+        <v>751426</v>
       </c>
       <c r="R45" t="n">
-        <v>7216039</v>
+        <v>7215728</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5641,10 +5641,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118967384</v>
+        <v>118967351</v>
       </c>
       <c r="B46" t="n">
-        <v>91780</v>
+        <v>91802</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5657,21 +5657,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>751387</v>
+        <v>751417</v>
       </c>
       <c r="R46" t="n">
-        <v>7215965</v>
+        <v>7215928</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5753,7 +5753,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118966801</v>
+        <v>118967384</v>
       </c>
       <c r="B47" t="n">
         <v>91780</v>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>751425</v>
+        <v>751387</v>
       </c>
       <c r="R47" t="n">
-        <v>7215914</v>
+        <v>7215965</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5865,7 +5865,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118968115</v>
+        <v>118966665</v>
       </c>
       <c r="B48" t="n">
         <v>91780</v>
@@ -5905,10 +5905,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>751449</v>
+        <v>751413</v>
       </c>
       <c r="R48" t="n">
-        <v>7216169</v>
+        <v>7215913</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5977,10 +5977,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118967904</v>
+        <v>118968543</v>
       </c>
       <c r="B49" t="n">
-        <v>91412</v>
+        <v>96814</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5989,25 +5989,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4745</v>
+        <v>221941</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>751433</v>
+        <v>751544</v>
       </c>
       <c r="R49" t="n">
-        <v>7216048</v>
+        <v>7215969</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6089,10 +6089,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118967968</v>
+        <v>118967018</v>
       </c>
       <c r="B50" t="n">
-        <v>91780</v>
+        <v>91412</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6105,21 +6105,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>751409</v>
+        <v>751426</v>
       </c>
       <c r="R50" t="n">
-        <v>7216099</v>
+        <v>7215942</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6201,10 +6201,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118966665</v>
+        <v>118966618</v>
       </c>
       <c r="B51" t="n">
-        <v>91780</v>
+        <v>91412</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6217,21 +6217,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>751413</v>
+        <v>751464</v>
       </c>
       <c r="R51" t="n">
-        <v>7215913</v>
+        <v>7215896</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
